--- a/output/pdf_financials_xlsx/BIG.xlsx
+++ b/output/pdf_financials_xlsx/BIG.xlsx
@@ -982,7 +982,7 @@
         <v>-0.149587</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.041104</v>
+        <v>-0.041104</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>-0.97749</v>
@@ -1154,7 +1154,7 @@
         <v>-0.149587</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.041104</v>
+        <v>-0.041104</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>-0.97749</v>
@@ -1271,7 +1271,7 @@
         <v>-0.149587</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.041104</v>
+        <v>-0.041104</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>-0.97749</v>
@@ -1423,7 +1423,7 @@
         <v>-0.149587</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.041104</v>
+        <v>-0.041104</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-0.97749</v>
@@ -1501,7 +1501,7 @@
         <v>-0.149587</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.041104</v>
+        <v>-0.041104</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-0.97749</v>
@@ -1587,7 +1587,7 @@
         <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>-0</v>
@@ -3555,25 +3555,25 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.065332</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.065332</v>
       </c>
       <c r="D92" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.278832</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.102784</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>5.104257</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>4.400042</v>
       </c>
       <c r="I92" s="3" t="n">
         <v>0</v>
@@ -3751,7 +3751,7 @@
         <v>-0.149587</v>
       </c>
       <c r="C99" s="3" t="n">
-        <v>0.041104</v>
+        <v>-0.041104</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>-0.97749</v>
@@ -5628,7 +5628,11 @@
           <t>Warrants reserve (Note 12)</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
@@ -6524,7 +6528,11 @@
           <t>Warrant reserve (Note 13)</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
@@ -6952,7 +6960,11 @@
           <t>Warrant reserve (Note 8)</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>-</t>
@@ -7602,7 +7614,11 @@
           <t>Warrant reserve 4</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>-</t>
@@ -8784,7 +8800,11 @@
           <t>Share-based payments reserve (note 4)</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E71" s="5" t="n">
         <v>0.065332</v>
       </c>
@@ -21571,10 +21591,10 @@
         </is>
       </c>
       <c r="F302" s="5" t="n">
-        <v>0.041104</v>
+        <v>-0.041104</v>
       </c>
       <c r="G302" s="5" t="n">
-        <v>0.049093</v>
+        <v>-0.049093</v>
       </c>
       <c r="H302" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/BIG.xlsx
+++ b/output/pdf_financials_xlsx/BIG.xlsx
@@ -829,10 +829,10 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.004206</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.000523</v>
       </c>
       <c r="F12" s="1" t="inlineStr">
         <is>
@@ -1426,10 +1426,10 @@
         <v>-0.041104</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.97749</v>
+        <v>-0.981696</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-7.080949</v>
+        <v>-7.081472</v>
       </c>
       <c r="F27" s="1" t="inlineStr">
         <is>
@@ -1504,10 +1504,10 @@
         <v>-0.041104</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.97749</v>
+        <v>-0.981696</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-7.080949</v>
+        <v>-7.081472</v>
       </c>
       <c r="F29" s="1" t="inlineStr">
         <is>
@@ -1677,16 +1677,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.31033</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.269716</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.691421</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>1.835699</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>1.802284</v>
@@ -1739,16 +1739,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.31033</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.269716</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.691421</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>1.835699</v>
       </c>
       <c r="F36" s="3" t="n">
         <v>1.802284</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -7174,7 +7174,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -7956,7 +7956,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -8520,7 +8520,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E66" s="5" t="n">
@@ -20480,7 +20480,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">

--- a/output/pdf_financials_xlsx/BIG.xlsx
+++ b/output/pdf_financials_xlsx/BIG.xlsx
@@ -2648,19 +2648,19 @@
         <v>0</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.067855</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>0.412429</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>0.152212</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>0.658842</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>0.797534</v>
       </c>
     </row>
     <row r="65">
@@ -2741,19 +2741,19 @@
         <v>0</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.065955</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.10478</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.352718</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.0856</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.381976</v>
       </c>
     </row>
     <row r="68">
